--- a/backend/excel/activity_logs.xlsx
+++ b/backend/excel/activity_logs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H94"/>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,159 +461,163 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>log_cdf3f5f6e62d</t>
+          <t>log_9c693cd798f1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>emp_d33f6d07baa5</t>
+          <t>emp_9370c1d0a3e4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jane Employee</t>
+          <t>prasanna</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>login</t>
+          <t>update</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>jane1480f4@crm.com</t>
-        </is>
-      </c>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>prj_86065138d368</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:28</t>
+          <t>2026-10-07 18:58:31</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>log_2261f745d435</t>
+          <t>log_2b4c8e41abd0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>emp_d33f6d07baa5</t>
+          <t>emp_9370c1d0a3e4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jane Employee</t>
+          <t>prasanna</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>/api/employees</t>
+          <t>/api/projects/prj_86065138d368</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:28</t>
+          <t>2026-10-07 18:58:31</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>log_758faec01175</t>
+          <t>log_47c4198d9d2a</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>emp_8a7467e2e5b2</t>
+          <t>emp_9370c1d0a3e4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>John Dev</t>
+          <t>prasanna</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>login</t>
+          <t>assign</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>lead_fe1ae72b28ae</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>john1480f4@crm.com</t>
+          <t>unassigned</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:29</t>
+          <t>2026-10-07 18:58:31</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>log_707763d2229c</t>
+          <t>log_c29a173437eb</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp_8a7467e2e5b2</t>
+          <t>emp_9370c1d0a3e4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>John Dev</t>
+          <t>prasanna</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>/api/leads/lead_fe1ae72b28ae</t>
+          <t>/api/leads/lead_fe1ae72b28ae/assign</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:29</t>
+          <t>2026-10-07 18:58:31</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>log_4e18f5b537b0</t>
+          <t>log_2ea03aca8089</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -628,34 +632,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>role_1a0212897e96</t>
-        </is>
-      </c>
+          <t>/api/projects/tasks/tsk_df297d0973e6</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Growth Hacker (access: employee)</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:29</t>
+          <t>2026-10-07 18:58:31</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>log_562cc35cfeef</t>
+          <t>log_c265aa61d38b</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -670,30 +670,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>update</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>/api/roles</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>prj_86065138d368</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:29</t>
+          <t>2026-10-07 18:58:31</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>log_59ecd1df661d</t>
+          <t>log_579c4bbb7eb0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -708,30 +708,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>/api/roles</t>
+          <t>/api/projects/prj_86065138d368</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:29</t>
+          <t>2026-10-07 18:58:31</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>log_c7a5da5878a7</t>
+          <t>log_fe6ae86f9af0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -746,34 +746,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>assign</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>employee</t>
+          <t>lead</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>emp_a87f66a2153c</t>
+          <t>lead_fe1ae72b28ae</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>rita1480f4@crm.com</t>
+          <t>emp_d33f6d07baa5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:29</t>
+          <t>2026-10-07 18:58:32</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>log_7e8e23c265b6</t>
+          <t>log_24f55953f652</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -793,25 +793,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>/api/employees</t>
+          <t>/api/leads/lead_fe1ae72b28ae/assign</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:29</t>
+          <t>2026-10-07 18:58:32</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>log_3a56963ae445</t>
+          <t>log_6a02b3249775</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -826,78 +826,82 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>create</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>/api/employees</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>lead_a72d835f5738</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>Second Buyer</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:29</t>
+          <t>2026-10-07 18:58:32</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>log_ab9862c7e2d2</t>
+          <t>log_9b219481236f</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>emp_a87f66a2153c</t>
+          <t>emp_9370c1d0a3e4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rita Role</t>
+          <t>prasanna</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>login</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>auth</t>
+          <t>/api/leads</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>rita1480f4@crm.com</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:29</t>
+          <t>2026-10-07 18:58:32</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>log_a99524b59437</t>
+          <t>log_a7ee466de0ab</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>emp_a87f66a2153c</t>
+          <t>emp_d33f6d07baa5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rita Role</t>
+          <t>Jane Employee</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -907,7 +911,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>/api/roles</t>
+          <t>/api/leads/lead_fe1ae72b28ae/assign</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -918,302 +922,298 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:29</t>
+          <t>2026-10-07 18:58:32</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>log_fdf04ce22925</t>
+          <t>log_16ef01b0a338</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>emp_9370c1d0a3e4</t>
+          <t>emp_d33f6d07baa5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>prasanna</t>
+          <t>Jane Employee</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>/api/roles/role_1a0212897e96</t>
+          <t>/api/leads/lead_a72d835f5738</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>404</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:29</t>
+          <t>2026-10-07 18:58:32</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>log_088d923f7316</t>
+          <t>log_1a49f90bf81c</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>emp_9370c1d0a3e4</t>
+          <t>emp_d33f6d07baa5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>prasanna</t>
+          <t>Jane Employee</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>employee</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>emp_a87f66a2153c</t>
-        </is>
-      </c>
+          <t>/api/leads/lead_a72d835f5738</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>rita1480f4@crm.com</t>
+          <t>404</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:29</t>
+          <t>2026-10-07 18:58:32</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>log_820e843b8a24</t>
+          <t>log_f89afdcc5f65</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>emp_9370c1d0a3e4</t>
+          <t>emp_d33f6d07baa5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>prasanna</t>
+          <t>Jane Employee</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>create</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>/api/employees/emp_a87f66a2153c</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>lead_2cab95becb19</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>Jane Own Lead</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:30</t>
+          <t>2026-10-07 18:58:33</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>log_2c4979597ef8</t>
+          <t>log_e6bf19a72432</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>emp_9370c1d0a3e4</t>
+          <t>emp_d33f6d07baa5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>prasanna</t>
+          <t>Jane Employee</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>role_1a0212897e96</t>
-        </is>
-      </c>
+          <t>/api/leads</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Growth Hacker</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:30</t>
+          <t>2026-10-07 18:58:33</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>log_4b3957955d73</t>
+          <t>log_303f7e455964</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>emp_9370c1d0a3e4</t>
+          <t>emp_8a7467e2e5b2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>prasanna</t>
+          <t>John Dev</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>create</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>/api/roles/role_1a0212897e96</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>lead_f1ffb3d7de50</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>Dev Own Lead</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:30</t>
+          <t>2026-10-07 18:58:33</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>log_8b3d4572a2a2</t>
+          <t>log_0ca4ff5e30b6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>emp_9370c1d0a3e4</t>
+          <t>emp_8a7467e2e5b2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>prasanna</t>
+          <t>John Dev</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>/api/roles/role_46052807f7bb</t>
+          <t>/api/leads</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:30</t>
+          <t>2026-10-07 18:58:33</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>log_b033ecaa9084</t>
+          <t>log_092a68a7e8c3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>emp_9370c1d0a3e4</t>
+          <t>emp_8a7467e2e5b2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>prasanna</t>
+          <t>John Dev</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>assign</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>lead</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>lead_fe1ae72b28ae</t>
-        </is>
-      </c>
+          <t>/api/leads/lead_f1ffb3d7de50/followups</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>emp_d33f6d07baa5</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:30</t>
+          <t>2026-10-07 18:58:33</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>log_918e91cd9464</t>
+          <t>log_fb69f62a7946</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>emp_9370c1d0a3e4</t>
+          <t>emp_8a7467e2e5b2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>prasanna</t>
+          <t>John Dev</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1223,139 +1223,143 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>/api/leads/lead_fe1ae72b28ae/assign</t>
+          <t>/api/leads/lead_fe1ae72b28ae/followups</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>404</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:30</t>
+          <t>2026-10-07 18:58:33</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>log_6359f80dd825</t>
+          <t>log_6916ed7af678</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>emp_9370c1d0a3e4</t>
+          <t>emp_8a7467e2e5b2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>prasanna</t>
+          <t>John Dev</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>/api/projects/prj_86065138d368/tasks</t>
+          <t>/api/leads/lead_fe1ae72b28ae</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>404</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:31</t>
+          <t>2026-10-07 18:58:33</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>log_9c693cd798f1</t>
+          <t>log_06a3423ab38b</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>emp_9370c1d0a3e4</t>
+          <t>emp_8a7467e2e5b2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>prasanna</t>
+          <t>John Dev</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>project</t>
+          <t>company</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>prj_86065138d368</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>cmp_7f1e032d66ac</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dev Co</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:31</t>
+          <t>2026-10-07 18:58:33</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>log_2b4c8e41abd0</t>
+          <t>log_b533b00ec6b4</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>emp_9370c1d0a3e4</t>
+          <t>emp_8a7467e2e5b2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>prasanna</t>
+          <t>John Dev</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>/api/projects/prj_86065138d368</t>
+          <t>/api/companies</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:31</t>
+          <t>2026-10-07 18:58:33</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>log_47c4198d9d2a</t>
+          <t>log_e924156ff3fa</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1370,34 +1374,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>assign</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>lead</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>lead_fe1ae72b28ae</t>
-        </is>
-      </c>
+          <t>/api/followups/fup_4b38b0ccb8e7</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>unassigned</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:31</t>
+          <t>2026-10-07 18:58:33</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>log_c29a173437eb</t>
+          <t>log_284f69344299</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1412,30 +1412,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>/api/leads/lead_fe1ae72b28ae/assign</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>lead_f1ffb3d7de50</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:31</t>
+          <t>2026-10-07 18:58:33</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>log_2ea03aca8089</t>
+          <t>log_5a29546af527</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>/api/projects/tasks/tsk_df297d0973e6</t>
+          <t>/api/leads/lead_f1ffb3d7de50</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -1466,14 +1466,14 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:31</t>
+          <t>2026-10-07 18:58:33</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>log_c265aa61d38b</t>
+          <t>log_5013c364e74c</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1488,30 +1488,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>project</t>
+          <t>company</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>prj_86065138d368</t>
+          <t>cmp_7f1e032d66ac</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:31</t>
+          <t>2026-10-07 18:58:34</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>log_579c4bbb7eb0</t>
+          <t>log_a654d15d47ab</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1526,12 +1526,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>/api/projects/prj_86065138d368</t>
+          <t>/api/companies/cmp_7f1e032d66ac</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -1542,136 +1542,128 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:31</t>
+          <t>2026-10-07 18:58:34</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>log_fe6ae86f9af0</t>
+          <t>log_608efd364b80</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>emp_9370c1d0a3e4</t>
+          <t>emp_d33f6d07baa5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>prasanna</t>
+          <t>Jane Employee</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>assign</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>lead</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>lead_fe1ae72b28ae</t>
-        </is>
-      </c>
+          <t>/api/leads/lead_fe1ae72b28ae/calls</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>emp_d33f6d07baa5</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:32</t>
+          <t>2026-10-07 18:58:34</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>log_24f55953f652</t>
+          <t>log_625bf766e390</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>emp_9370c1d0a3e4</t>
+          <t>emp_d33f6d07baa5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>prasanna</t>
+          <t>Jane Employee</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>/api/leads/lead_fe1ae72b28ae/assign</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>lead_2cab95becb19</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:32</t>
+          <t>2026-10-07 18:58:34</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>log_6a02b3249775</t>
+          <t>log_95c6923eec92</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>emp_9370c1d0a3e4</t>
+          <t>emp_d33f6d07baa5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>prasanna</t>
+          <t>Jane Employee</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>lead</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>lead_a72d835f5738</t>
-        </is>
-      </c>
+          <t>/api/leads/lead_2cab95becb19</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Second Buyer</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:32</t>
+          <t>2026-10-07 18:58:34</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>log_9b219481236f</t>
+          <t>log_90be0b7331d6</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1686,116 +1678,116 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>/api/leads</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>lead_a72d835f5738</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:32</t>
+          <t>2026-10-07 18:58:34</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>log_a7ee466de0ab</t>
+          <t>log_6990420d4228</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>emp_d33f6d07baa5</t>
+          <t>emp_9370c1d0a3e4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jane Employee</t>
+          <t>prasanna</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>/api/leads/lead_fe1ae72b28ae/assign</t>
+          <t>/api/leads/lead_a72d835f5738</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:32</t>
+          <t>2026-10-07 18:58:34</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>log_16ef01b0a338</t>
+          <t>log_77db9c5dcd55</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>emp_d33f6d07baa5</t>
+          <t>emp_9370c1d0a3e4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jane Employee</t>
+          <t>prasanna</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>/api/leads/lead_a72d835f5738</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>lead_fe1ae72b28ae</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:32</t>
+          <t>2026-10-07 18:58:34</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>log_1a49f90bf81c</t>
+          <t>log_00d8bd6edfbe</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>emp_d33f6d07baa5</t>
+          <t>emp_9370c1d0a3e4</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jane Employee</t>
+          <t>prasanna</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1805,157 +1797,149 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>/api/leads/lead_a72d835f5738</t>
+          <t>/api/leads/lead_fe1ae72b28ae</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:32</t>
+          <t>2026-10-07 18:58:35</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>log_f89afdcc5f65</t>
+          <t>log_5286b9ac3165</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>emp_d33f6d07baa5</t>
+          <t>emp_9370c1d0a3e4</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jane Employee</t>
+          <t>prasanna</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>lead</t>
+          <t>project</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>lead_2cab95becb19</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Jane Own Lead</t>
-        </is>
-      </c>
+          <t>prj_86065138d368</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:33</t>
+          <t>2026-10-07 18:58:35</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>log_e6bf19a72432</t>
+          <t>log_ec6e90929e5a</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>emp_d33f6d07baa5</t>
+          <t>emp_9370c1d0a3e4</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jane Employee</t>
+          <t>prasanna</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>/api/leads</t>
+          <t>/api/projects/prj_86065138d368</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:33</t>
+          <t>2026-10-07 18:58:35</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>log_303f7e455964</t>
+          <t>log_a65af17457eb</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>emp_8a7467e2e5b2</t>
+          <t>emp_d33f6d07baa5</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>John Dev</t>
+          <t>Jane Employee</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>lead</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>lead_f1ffb3d7de50</t>
-        </is>
-      </c>
+          <t>/api/auth/change-password</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dev Own Lead</t>
+          <t>403</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:33</t>
+          <t>2026-10-07 18:58:35</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>log_0ca4ff5e30b6</t>
+          <t>log_3c08fc82bd8d</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>emp_8a7467e2e5b2</t>
+          <t>emp_d33f6d07baa5</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>John Dev</t>
+          <t>Jane Employee</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1965,191 +1949,191 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>/api/leads</t>
+          <t>/api/auth/register</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>403</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:33</t>
+          <t>2026-10-07 18:58:35</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>log_092a68a7e8c3</t>
+          <t>log_aa64dbcbce34</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>emp_8a7467e2e5b2</t>
+          <t>emp_9370c1d0a3e4</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>John Dev</t>
+          <t>prasanna</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>/api/leads/lead_f1ffb3d7de50/followups</t>
+          <t>/api/auth/change-password</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:33</t>
+          <t>2026-10-07 18:58:35</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>log_fb69f62a7946</t>
+          <t>log_4a3be9fa3488</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>emp_8a7467e2e5b2</t>
+          <t>emp_9370c1d0a3e4</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>John Dev</t>
+          <t>prasanna</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>update</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>/api/leads/lead_fe1ae72b28ae/followups</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>emp_d33f6d07baa5</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>jane1480f4@crm.com</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:33</t>
+          <t>2026-10-07 18:58:36</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>log_6916ed7af678</t>
+          <t>log_0f4dc471f2cd</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>emp_8a7467e2e5b2</t>
+          <t>emp_9370c1d0a3e4</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>John Dev</t>
+          <t>prasanna</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>/api/leads/lead_fe1ae72b28ae</t>
+          <t>/api/employees/emp_d33f6d07baa5</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:33</t>
+          <t>2026-10-07 18:58:36</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>log_06a3423ab38b</t>
+          <t>log_5731b9536f66</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>emp_8a7467e2e5b2</t>
+          <t>emp_d33f6d07baa5</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>John Dev</t>
+          <t>Jane Employee</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>login</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>cmp_7f1e032d66ac</t>
-        </is>
-      </c>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dev Co</t>
+          <t>jane1480f4@crm.com</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:33</t>
+          <t>2026-10-07 18:58:36</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>log_b533b00ec6b4</t>
+          <t>log_3bec19eeec4f</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>emp_8a7467e2e5b2</t>
+          <t>emp_d33f6d07baa5</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>John Dev</t>
+          <t>Jane Employee</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2159,25 +2143,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>/api/companies</t>
+          <t>/api/auth/notifications</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>403</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:33</t>
+          <t>2026-10-07 18:58:36</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>log_e924156ff3fa</t>
+          <t>log_252155744f59</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2192,30 +2176,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>/api/followups/fup_4b38b0ccb8e7</t>
+          <t>/api/auth/notifications</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>404</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:33</t>
+          <t>2026-10-07 18:58:36</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>log_284f69344299</t>
+          <t>log_189cc3a77b9f</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2230,30 +2214,30 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>lead</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>lead_f1ffb3d7de50</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+          <t>/api/auth/notifications</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:33</t>
+          <t>2026-10-07 18:58:36</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>log_5a29546af527</t>
+          <t>log_99d7c86fd331</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2268,106 +2252,106 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>/api/leads/lead_f1ffb3d7de50</t>
+          <t>/api/auth/notifications</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:33</t>
+          <t>2026-10-07 18:58:36</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>log_5013c364e74c</t>
+          <t>log_1ab2935a3451</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>emp_9370c1d0a3e4</t>
+          <t>emp_d33f6d07baa5</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>prasanna</t>
+          <t>Jane Employee</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>cmp_7f1e032d66ac</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
+          <t>/api/auth/notifications/ntf_93b82277022e/reply</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:34</t>
+          <t>2026-10-07 18:58:37</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>log_a654d15d47ab</t>
+          <t>log_9c4cd85f6d4a</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>emp_9370c1d0a3e4</t>
+          <t>emp_8a7467e2e5b2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>prasanna</t>
+          <t>John Dev</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>/api/companies/cmp_7f1e032d66ac</t>
+          <t>/api/auth/notifications/ntf_93b82277022e/reply</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>404</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:34</t>
+          <t>2026-10-07 18:58:37</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>log_608efd364b80</t>
+          <t>log_62fff0dedbfb</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2387,139 +2371,139 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>/api/leads/lead_fe1ae72b28ae/calls</t>
+          <t>/api/auth/notifications/ntf_93b82277022e/reply</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>422</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:34</t>
+          <t>2026-10-07 18:58:37</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>log_625bf766e390</t>
+          <t>log_7c556bc48d19</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>emp_d33f6d07baa5</t>
+          <t>emp_9370c1d0a3e4</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jane Employee</t>
+          <t>prasanna</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>lead</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>lead_2cab95becb19</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
+          <t>/api/auth/notifications</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:34</t>
+          <t>2026-10-07 18:58:37</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>log_95c6923eec92</t>
+          <t>log_4b588d09cf63</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>emp_d33f6d07baa5</t>
+          <t>emp_8a7467e2e5b2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jane Employee</t>
+          <t>John Dev</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>/api/leads/lead_2cab95becb19</t>
+          <t>/api/auth/notifications/ntf_a7e2a0e13036/reply</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:34</t>
+          <t>2026-10-07 18:58:37</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>log_90be0b7331d6</t>
+          <t>log_0bc4ff5263b1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>emp_9370c1d0a3e4</t>
+          <t>emp_d33f6d07baa5</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>prasanna</t>
+          <t>Jane Employee</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>lead</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>lead_a72d835f5738</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+          <t>/api/leads/import</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:34</t>
+          <t>2026-10-07 18:58:37</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>log_6990420d4228</t>
+          <t>log_68469f094de1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2534,30 +2518,34 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>create</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>/api/leads/lead_a72d835f5738</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>lead_35495cde915b</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>Import One</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:34</t>
+          <t>2026-10-07 18:58:37</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>log_77db9c5dcd55</t>
+          <t>log_da4c14ab471d</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2572,7 +2560,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>create</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2582,20 +2570,24 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>lead_fe1ae72b28ae</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
+          <t>lead_c26aadac0bcb</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Import Two</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:34</t>
+          <t>2026-10-07 18:58:38</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>log_00d8bd6edfbe</t>
+          <t>log_e90f77fb363a</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2610,30 +2602,30 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>/api/leads/lead_fe1ae72b28ae</t>
+          <t>/api/leads/import</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:35</t>
+          <t>2026-10-07 18:58:38</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>log_5286b9ac3165</t>
+          <t>log_729f77568b39</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2648,30 +2640,30 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>project</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>prj_86065138d368</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
+          <t>/api/leads/import</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:35</t>
+          <t>2026-10-07 18:58:38</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>log_ec6e90929e5a</t>
+          <t>log_5b5ea3e1dcb3</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2686,78 +2678,82 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>/api/projects/prj_86065138d368</t>
+          <t>/api/leads/import</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>422</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:35</t>
+          <t>2026-10-07 18:58:38</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>log_a65af17457eb</t>
+          <t>log_ac54e5079eb0</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>emp_d33f6d07baa5</t>
+          <t>emp_9370c1d0a3e4</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Jane Employee</t>
+          <t>prasanna</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>create</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>/api/auth/change-password</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>lead_96c2405603d7</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>Import Three</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:35</t>
+          <t>2026-10-07 18:58:38</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>log_3c08fc82bd8d</t>
+          <t>log_20e1a8e0f254</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>emp_d33f6d07baa5</t>
+          <t>emp_9370c1d0a3e4</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jane Employee</t>
+          <t>prasanna</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2767,25 +2763,25 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>/api/auth/register</t>
+          <t>/api/leads/import</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:35</t>
+          <t>2026-10-07 18:58:38</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>log_aa64dbcbce34</t>
+          <t>log_fb4c54e7cc4c</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2800,30 +2796,30 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>/api/auth/change-password</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>lead_c26aadac0bcb</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:35</t>
+          <t>2026-10-07 18:58:38</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>log_4a3be9fa3488</t>
+          <t>log_3ee272421e7a</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2838,34 +2834,30 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>employee</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>emp_d33f6d07baa5</t>
-        </is>
-      </c>
+          <t>/api/leads/lead_c26aadac0bcb</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>jane1480f4@crm.com</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:36</t>
+          <t>2026-10-07 18:58:38</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>log_0f4dc471f2cd</t>
+          <t>log_162617117bd2</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2880,106 +2872,106 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>/api/employees/emp_d33f6d07baa5</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>lead_96c2405603d7</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:36</t>
+          <t>2026-10-07 18:58:39</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>log_5731b9536f66</t>
+          <t>log_9208dd22dd2e</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>emp_d33f6d07baa5</t>
+          <t>emp_9370c1d0a3e4</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Jane Employee</t>
+          <t>prasanna</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>login</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>auth</t>
+          <t>/api/leads/lead_96c2405603d7</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>jane1480f4@crm.com</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:36</t>
+          <t>2026-10-07 18:58:39</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>log_3bec19eeec4f</t>
+          <t>log_512b76299cce</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>emp_d33f6d07baa5</t>
+          <t>emp_9370c1d0a3e4</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jane Employee</t>
+          <t>prasanna</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>/api/auth/notifications</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>lead_35495cde915b</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:36</t>
+          <t>2026-10-07 18:58:39</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>log_252155744f59</t>
+          <t>log_136269b71fac</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2994,30 +2986,30 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>/api/auth/notifications</t>
+          <t>/api/leads/lead_35495cde915b</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:36</t>
+          <t>2026-10-07 18:58:39</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>log_189cc3a77b9f</t>
+          <t>log_3a339d42e18c</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3032,30 +3024,30 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>/api/auth/notifications</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
-      </c>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>cmp_489d017df396</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:36</t>
+          <t>2026-10-07 18:58:39</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>log_99d7c86fd331</t>
+          <t>log_6789b9e666d5</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3070,144 +3062,152 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>/api/auth/notifications</t>
+          <t>/api/companies/cmp_489d017df396</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:36</t>
+          <t>2026-10-07 18:58:39</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>log_1ab2935a3451</t>
+          <t>log_4ace2ec6580e</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t>emp_d33f6d07baa5</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Jane Employee</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>/api/auth/notifications/ntf_93b82277022e/reply</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>jane1480f4@crm.com</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:37</t>
+          <t>2026-10-07 18:58:39</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>log_9c4cd85f6d4a</t>
+          <t>log_7b7213995658</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>emp_8a7467e2e5b2</t>
+          <t>emp_9370c1d0a3e4</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>John Dev</t>
+          <t>prasanna</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>/api/auth/notifications/ntf_93b82277022e/reply</t>
+          <t>/api/employees/emp_d33f6d07baa5</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:37</t>
+          <t>2026-10-07 18:58:39</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>log_62fff0dedbfb</t>
+          <t>log_06772c90bd19</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>emp_d33f6d07baa5</t>
+          <t>emp_9370c1d0a3e4</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Jane Employee</t>
+          <t>prasanna</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>/api/auth/notifications/ntf_93b82277022e/reply</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>emp_8a7467e2e5b2</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>john1480f4@crm.com</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:37</t>
+          <t>2026-10-07 18:58:39</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>log_7c556bc48d19</t>
+          <t>log_c7b90af10000</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3222,106 +3222,106 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>/api/auth/notifications</t>
+          <t>/api/employees/emp_8a7467e2e5b2</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:37</t>
+          <t>2026-10-07 18:58:39</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>log_4b588d09cf63</t>
+          <t>log_54b76ab5eee8</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>emp_8a7467e2e5b2</t>
+          <t>emp_9370c1d0a3e4</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>John Dev</t>
+          <t>prasanna</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>login</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>/api/auth/notifications/ntf_a7e2a0e13036/reply</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>admin@crm.com</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:37</t>
+          <t>2026-10-08 10:35:52</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>log_0bc4ff5263b1</t>
+          <t>log_d91c16e5c8f5</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>emp_d33f6d07baa5</t>
+          <t>emp_9370c1d0a3e4</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Jane Employee</t>
+          <t>prasanna</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>login</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>/api/leads/import</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>admin@crm.com</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:37</t>
+          <t>2026-10-08 10:40:42</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>log_68469f094de1</t>
+          <t>log_aa76b159368d</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3346,24 +3346,24 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>lead_35495cde915b</t>
+          <t>lead_3b826568ba91</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Import One</t>
+          <t>tcs</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:37</t>
+          <t>2026-10-08 10:42:51</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>log_da4c14ab471d</t>
+          <t>log_7f7e5c759872</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3378,82 +3378,78 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>login</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>lead</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>lead_c26aadac0bcb</t>
-        </is>
-      </c>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Import Two</t>
+          <t>admin@crm.com</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:38</t>
+          <t>2026-10-08 10:51:22</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>log_e90f77fb363a</t>
+          <t>log_b6ad732d6c48</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>emp_9370c1d0a3e4</t>
+          <t>emp_3dbe82c7aa1d</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>prasanna</t>
+          <t>jeeva</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>login</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>/api/leads/import</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>jeeva@gmail.com</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:38</t>
+          <t>2026-10-08 10:53:16</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>log_729f77568b39</t>
+          <t>log_e084e04e5719</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>emp_9370c1d0a3e4</t>
+          <t>emp_3dbe82c7aa1d</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>prasanna</t>
+          <t>jeeva</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3463,25 +3459,25 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>/api/leads/import</t>
+          <t>/api/leads/lead_2f8d3eba4432/followups</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:38</t>
+          <t>2026-10-08 10:54:21</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>log_5b5ea3e1dcb3</t>
+          <t>log_2e5d9f5f89c2</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3496,30 +3492,30 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>login</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>/api/leads/import</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>admin@crm.com</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:38</t>
+          <t>2026-10-08 10:54:42</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>log_ac54e5079eb0</t>
+          <t>log_195b58a41e53</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3534,34 +3530,30 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>lead</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>lead_96c2405603d7</t>
-        </is>
-      </c>
+          <t>/api/followups/fup_af9e1ebed0fa</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Import Three</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:38</t>
+          <t>2026-10-08 10:55:10</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>log_20e1a8e0f254</t>
+          <t>log_bbf7c45edc4b</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3576,30 +3568,30 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>/api/leads/import</t>
+          <t>/api/followups/fup_af9e1ebed0fa</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:38</t>
+          <t>2026-10-08 10:55:11</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>log_fb4c54e7cc4c</t>
+          <t>log_ec4fb1d46bf8</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3614,30 +3606,30 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>lead</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>lead_c26aadac0bcb</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr"/>
+          <t>/api/followups/fup_af9e1ebed0fa</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:38</t>
+          <t>2026-10-08 10:55:11</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>log_3ee272421e7a</t>
+          <t>log_7723d7a64f6b</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3652,68 +3644,68 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>/api/leads/lead_c26aadac0bcb</t>
+          <t>/api/auth/notifications</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:38</t>
+          <t>2026-10-08 10:55:58</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>log_162617117bd2</t>
+          <t>log_1c76dc8e64cc</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>emp_9370c1d0a3e4</t>
+          <t>emp_20205e6cffa7</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>prasanna</t>
+          <t>logesh</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>login</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>lead</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>lead_96c2405603d7</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr"/>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>logesh@gmail.com</t>
+        </is>
+      </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:39</t>
+          <t>2026-10-08 10:56:32</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>log_9208dd22dd2e</t>
+          <t>log_552d92e58f3d</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3728,68 +3720,68 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>login</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>/api/leads/lead_96c2405603d7</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>admin@crm.com</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:39</t>
+          <t>2026-10-08 11:18:29</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>log_512b76299cce</t>
+          <t>log_0f85811e0460</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>emp_9370c1d0a3e4</t>
+          <t>emp_3dbe82c7aa1d</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>prasanna</t>
+          <t>jeeva</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>login</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>lead</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>lead_35495cde915b</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr"/>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>jeeva@gmail.com</t>
+        </is>
+      </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:39</t>
+          <t>2026-10-08 11:26:35</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>log_136269b71fac</t>
+          <t>log_f47107fc3d80</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3804,259 +3796,61 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>login</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>/api/leads/lead_35495cde915b</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>admin@crm.com</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:39</t>
+          <t>2026-10-08 11:46:39</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>log_3a339d42e18c</t>
+          <t>log_312add75a83e</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>emp_9370c1d0a3e4</t>
+          <t>emp_3dbe82c7aa1d</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>prasanna</t>
+          <t>jeeva</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>login</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>cmp_489d017df396</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr"/>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>jeeva@gmail.com</t>
+        </is>
+      </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:39</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>log_6789b9e666d5</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>emp_9370c1d0a3e4</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>prasanna</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>DELETE</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>/api/companies/cmp_489d017df396</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>2026-10-07 18:58:39</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>log_4ace2ec6580e</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>emp_9370c1d0a3e4</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>prasanna</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>delete</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>employee</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>emp_d33f6d07baa5</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>jane1480f4@crm.com</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>2026-10-07 18:58:39</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>log_7b7213995658</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>emp_9370c1d0a3e4</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>prasanna</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>DELETE</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>/api/employees/emp_d33f6d07baa5</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>2026-10-07 18:58:39</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>log_06772c90bd19</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>emp_9370c1d0a3e4</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>prasanna</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>delete</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>employee</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>emp_8a7467e2e5b2</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>john1480f4@crm.com</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>2026-10-07 18:58:39</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>log_c7b90af10000</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>emp_9370c1d0a3e4</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>prasanna</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>DELETE</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>/api/employees/emp_8a7467e2e5b2</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>2026-10-07 18:58:39</t>
+          <t>2026-10-08 11:51:42</t>
         </is>
       </c>
     </row>

--- a/backend/excel/activity_logs.xlsx
+++ b/backend/excel/activity_logs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,6 +458,3566 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>log_820233dff929</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Jane Employee</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>jane21d3d8@crm.com</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>log_bd956933f656</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Jane Employee</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>/api/employees</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>log_5148ee627a95</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>emp_24510a41c1f3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>John Dev</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>john21d3d8@crm.com</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>log_d7b63a5a43e8</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>emp_24510a41c1f3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>John Dev</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>/api/leads/lead_dc551388df48</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>log_400288bd8642</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>role_dd4f566dc16e</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Growth Hacker (access: employee)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>log_c6e777f89115</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>/api/roles</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>log_e2b6d4896a65</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>/api/roles</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>log_0ad719e79aa2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>emp_18e054d837d5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>rita21d3d8@crm.com</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>log_00e91cc3875b</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>/api/employees</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>log_5ee520c996cc</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>/api/employees</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>log_3a9b76e8b15c</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>emp_18e054d837d5</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Rita Role</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>rita21d3d8@crm.com</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>log_25932c78e68c</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>emp_18e054d837d5</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Rita Role</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>/api/roles</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>log_0ca19f4a5b6c</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>/api/roles/role_dd4f566dc16e</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>log_0e3fb8206c55</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>emp_18e054d837d5</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>rita21d3d8@crm.com</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>log_1ff2ccd694eb</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>/api/employees/emp_18e054d837d5</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>log_0bd848f3a055</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>role_dd4f566dc16e</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Growth Hacker</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>log_9974655bfa1e</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>/api/roles/role_dd4f566dc16e</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>log_f3ecc5e181f0</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>/api/roles/role_46052807f7bb</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>log_48a423daac79</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>assign</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>lead_dc551388df48</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>log_dc24594e33f8</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>/api/leads/lead_dc551388df48/assign</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>log_48aae618b567</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>/api/projects/prj_12311d0ebd08/tasks</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>log_040fa589aad6</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>prj_12311d0ebd08</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>log_23e381e80550</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>/api/projects/prj_12311d0ebd08</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>log_fd93b756b296</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>assign</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>lead_dc551388df48</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>unassigned</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>log_dde16d11d528</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>/api/leads/lead_dc551388df48/assign</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>log_6bc99ff17691</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>/api/projects/tasks/tsk_ea4d65a6bd5b</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>log_320ec3455a12</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>prj_12311d0ebd08</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>log_e21b16bc8837</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>/api/projects/prj_12311d0ebd08</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>log_49baf5d2f875</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>assign</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>lead_dc551388df48</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>log_86731705a23f</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>/api/leads/lead_dc551388df48/assign</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>log_ea53daf56799</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>lead_d523a36e791b</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Second Buyer</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>log_81b641f4fcb9</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>/api/leads</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>log_e2a091b9ed6f</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Jane Employee</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>/api/leads/lead_dc551388df48/assign</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>log_cb5876eace83</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Jane Employee</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>/api/leads/lead_d523a36e791b</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>log_38a53fbf4f3a</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Jane Employee</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>/api/leads/lead_d523a36e791b</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>log_b37fe6591dc9</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Jane Employee</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>lead_0ccd9e153319</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Jane Own Lead</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>log_31691a469026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Jane Employee</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>/api/leads</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>log_5de7644c53cd</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>emp_24510a41c1f3</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>John Dev</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>lead_1821500c5258</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dev Own Lead</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>log_656bf9ab55ac</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>emp_24510a41c1f3</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>John Dev</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>/api/leads</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>log_444303a3c424</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>emp_24510a41c1f3</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>John Dev</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>/api/leads/lead_1821500c5258/followups</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>log_231a1c0f6daa</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>emp_24510a41c1f3</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>John Dev</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>/api/leads/lead_dc551388df48/followups</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>log_87cdaf31e86b</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp_24510a41c1f3</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>John Dev</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>/api/leads/lead_dc551388df48</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>log_b6b14cb32555</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>emp_24510a41c1f3</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>John Dev</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>cmp_a981b414a019</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Dev Co</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>log_42f4e4ca3ef5</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>emp_24510a41c1f3</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>John Dev</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>/api/companies</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>log_7c11ee315294</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>/api/followups/fup_845205f99858</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>log_d901452e0bbc</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>lead_1821500c5258</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>log_854f63045f76</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>/api/leads/lead_1821500c5258</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>log_408b26f819f1</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>cmp_a981b414a019</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>log_027d30cba20c</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>/api/companies/cmp_a981b414a019</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>log_408ceaab7b29</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Jane Employee</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>/api/leads/lead_dc551388df48/calls</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>log_79db32457c0c</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Jane Employee</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>lead_0ccd9e153319</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>log_1166f961ddc6</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Jane Employee</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>/api/leads/lead_0ccd9e153319</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>log_9d0b5a4421fb</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>lead_d523a36e791b</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>log_33d560a51657</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>/api/leads/lead_d523a36e791b</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>log_9efcb2c3504f</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>lead_dc551388df48</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>log_e3a940f3e7db</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>/api/leads/lead_dc551388df48</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>log_d489c34f3c7e</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>prj_12311d0ebd08</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>log_1d50ef1bc9c5</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>/api/projects/prj_12311d0ebd08</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>log_0a924fec14e2</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Jane Employee</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>/api/auth/change-password</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>log_84a2d3432173</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Jane Employee</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>/api/auth/register</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>log_0b70da3d8d99</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>/api/auth/change-password</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>log_c2ea9b4864c5</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>jane21d3d8@crm.com</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>log_999e267a94cf</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>/api/employees/emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>log_8053eb3bbdfa</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Jane Employee</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>jane21d3d8@crm.com</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>log_c8c0e42dfeb0</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Jane Employee</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>/api/auth/notifications</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>log_17bf2a63a9fb</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>/api/auth/notifications</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>log_212ecb56f757</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>/api/auth/notifications</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>log_95e35d1977e8</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>/api/auth/notifications</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>log_d34760f37368</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Jane Employee</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>/api/auth/notifications/ntf_531f25a8e3f8/reply</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>log_eab9c01ee386</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>emp_24510a41c1f3</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>John Dev</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>/api/auth/notifications/ntf_531f25a8e3f8/reply</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>log_6761f1ab49dc</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Jane Employee</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>/api/auth/notifications/ntf_531f25a8e3f8/reply</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>log_9c6311e100a4</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>/api/auth/notifications</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>log_eba0780b22ea</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>emp_24510a41c1f3</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>John Dev</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>/api/auth/notifications/ntf_37a01376094b/reply</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>log_802ff7d742da</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Jane Employee</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>/api/leads/import</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>log_2ca86e03d427</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>lead_6722b6ab745e</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Import One</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>log_d4f7ea182031</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>lead_8eb4a3d111e9</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Import Two</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>log_dc03f137482d</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>/api/leads/import</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>log_e3cfbf19cd02</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>/api/leads/import</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>log_6015f307189f</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>/api/leads/import</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>log_ee29d8cfe993</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>lead_c2f5b38da613</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Import Three</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>log_a3cef4dc9b63</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>/api/leads/import</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>log_557391be43ce</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>lead_c2f5b38da613</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>log_33a50a9b4782</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>/api/leads/lead_c2f5b38da613</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>log_e71427cdfa46</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>lead_6722b6ab745e</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>log_3e13a1173e4c</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>/api/leads/lead_6722b6ab745e</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>log_1f8362cb0055</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>lead_8eb4a3d111e9</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>log_21b966b80c43</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>/api/leads/lead_8eb4a3d111e9</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>log_854a568a966d</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>cmp_93eb4562793d</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>log_3662c7dc0306</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>/api/companies/cmp_93eb4562793d</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>log_bb267e3096fc</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>jane21d3d8@crm.com</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>log_4f5983a09520</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>/api/employees/emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>log_4d191bf15870</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>prasanna</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>/api/employees/emp_24510a41c1f3</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:54</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
